--- a/main/ig/ConceptMap-mos-cdl.xlsx
+++ b/main/ig/ConceptMap-mos-cdl.xlsx
@@ -35,7 +35,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.0</t>
+    <t>3.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T07:40:33+00:00</t>
+    <t>2026-07-21T12:38:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -83,7 +83,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>
@@ -125,7 +125,7 @@
     <t/>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|2.0.1</t>
   </si>
   <si>
     <t>Contact.IdContact</t>
@@ -161,7 +161,7 @@
     <t>RelatedPerson.name.given</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|2.0.1</t>
   </si>
   <si>
     <t>Professionnel.idPP</t>
@@ -197,7 +197,7 @@
     <t>PractitionerRole.code</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.0.1</t>
   </si>
   <si>
     <t>EntiteGeographique.numFINESS</t>
@@ -230,7 +230,7 @@
     <t>Organization.name</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.0.1</t>
   </si>
   <si>
     <t>PersonnePriseEnCharge.idPersonnePriseEnCharge</t>
@@ -269,7 +269,7 @@
     <t>Patient.name.given</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Device</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Device|4.0.1</t>
   </si>
   <si>
     <t>RessourceMaterielle.libelle</t>

--- a/main/ig/ConceptMap-mos-cdl.xlsx
+++ b/main/ig/ConceptMap-mos-cdl.xlsx
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T12:38:43+00:00</t>
+    <t>2026-07-21T13:00:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ConceptMap-mos-cdl.xlsx
+++ b/main/ig/ConceptMap-mos-cdl.xlsx
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T13:00:31+00:00</t>
+    <t>2026-07-21T13:21:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ConceptMap-mos-cdl.xlsx
+++ b/main/ig/ConceptMap-mos-cdl.xlsx
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T13:21:42+00:00</t>
+    <t>2026-07-21T13:26:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
